--- a/compiler_practice_times.xlsx
+++ b/compiler_practice_times.xlsx
@@ -37,13 +37,13 @@
     <t xml:space="preserve">Intel C</t>
   </si>
   <si>
-    <t xml:space="preserve">O0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Os</t>
+    <t xml:space="preserve">-O0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-О2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Os</t>
   </si>
   <si>
     <t xml:space="preserve">Среднее (мкс)</t>
@@ -70,6 +70,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -92,12 +93,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -404,8 +407,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="10.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="10.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="3" width="10.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16380" min="16380" style="3" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="3" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
